--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:15</t>
+    <t xml:space="preserve">2026-09-09 22:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:15</t>
+    <t xml:space="preserve">2026-09-17 13:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8.66</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="3">
@@ -1115,26 +1115,26 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12.15</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>14.71</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9.26</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="7">
@@ -1175,35 +1175,35 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.25</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>9.08</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8.66</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="5">
@@ -1241,101 +1241,101 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>12.99</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>12.56</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>12.15</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>16.84</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>16.19</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>14.71</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9.85</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9.68</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>9.26</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="17">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:42</t>
+    <t xml:space="preserve">2026-09-25 21:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -536,7 +536,7 @@
         <v>-0.27</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2.47</v>
+        <v>-2.45</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>7</v>
@@ -556,10 +556,10 @@
         <v>7.67</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6.91</v>
+        <v>-6.84</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>7</v>
@@ -582,7 +582,7 @@
         <v>-0.42</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4.63</v>
+        <v>-4.58</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>7</v>
@@ -605,7 +605,7 @@
         <v>-0.36</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3.17</v>
+        <v>-3.19</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>6</v>
@@ -625,10 +625,10 @@
         <v>8.23</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5.47</v>
+        <v>-5.54</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>6</v>
@@ -651,7 +651,7 @@
         <v>-0.42</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4.34</v>
+        <v>-4.35</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>6</v>
@@ -674,7 +674,7 @@
         <v>-0.3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2.5</v>
+        <v>-2.51</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>5</v>
@@ -697,7 +697,7 @@
         <v>-0.51</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5.88</v>
+        <v>-5.91</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5</v>
@@ -717,10 +717,10 @@
         <v>10.18</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4.22</v>
+        <v>-4.17</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5</v>
@@ -743,7 +743,7 @@
         <v>-0.02</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>4</v>
@@ -766,7 +766,7 @@
         <v>-0.66</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7.31</v>
+        <v>-7.33</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>4</v>
@@ -789,7 +789,7 @@
         <v>-0.4</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3.66</v>
+        <v>-3.67</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>4</v>
@@ -809,10 +809,10 @@
         <v>13.58</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>3</v>
@@ -835,7 +835,7 @@
         <v>-0.41</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4.31</v>
+        <v>-4.35</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>-0.23</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2.03</v>
+        <v>-2.05</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3</v>
@@ -881,7 +881,7 @@
         <v>0.01</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>2</v>
@@ -901,10 +901,10 @@
         <v>10.77</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-6.59</v>
+        <v>-6.67</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>2</v>
@@ -927,7 +927,7 @@
         <v>-0.41</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3.26</v>
+        <v>-3.27</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>2</v>
@@ -950,7 +950,7 @@
         <v>-1.06</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-5.56</v>
+        <v>-5.58</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1</v>
@@ -973,7 +973,7 @@
         <v>-1.75</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-12.36</v>
+        <v>-12.35</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>-1.48</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-9.14</v>
+        <v>-9.12</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_metropolitana.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:40</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
